--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.07002728520886</v>
+        <v>3.58637943384644</v>
       </c>
       <c r="D2" t="n">
-        <v>18.49969517088918</v>
+        <v>3.006200465269492</v>
       </c>
       <c r="E2" t="n">
-        <v>8.781177996797858</v>
+        <v>1.426941424479652</v>
       </c>
       <c r="F2" t="n">
-        <v>7.892301056613245</v>
+        <v>1.282498921699653</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.82377820017236</v>
+        <v>7.121363957528008</v>
       </c>
       <c r="D3" t="n">
-        <v>10.54751155486449</v>
+        <v>1.71397062766548</v>
       </c>
       <c r="E3" t="n">
-        <v>8.781177996797858</v>
+        <v>1.426941424479652</v>
       </c>
       <c r="F3" t="n">
-        <v>7.892301056613245</v>
+        <v>1.282498921699653</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.19786054860269</v>
+        <v>2.632152339147937</v>
       </c>
       <c r="D4" t="n">
-        <v>16.1065979189553</v>
+        <v>2.617322161830236</v>
       </c>
       <c r="E4" t="n">
-        <v>8.781177996797858</v>
+        <v>1.426941424479652</v>
       </c>
       <c r="F4" t="n">
-        <v>7.892301056613245</v>
+        <v>1.282498921699653</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.79593546729059</v>
+        <v>5.816839513434721</v>
       </c>
       <c r="D5" t="n">
-        <v>30.4138126514911</v>
+        <v>4.942244555867304</v>
       </c>
       <c r="E5" t="n">
-        <v>8.781177996797858</v>
+        <v>1.426941424479652</v>
       </c>
       <c r="F5" t="n">
-        <v>7.892301056613245</v>
+        <v>1.282498921699653</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.7005746773389</v>
+        <v>4.501343385067571</v>
       </c>
       <c r="D6" t="n">
-        <v>27.80519874415598</v>
+        <v>4.518344795925348</v>
       </c>
       <c r="E6" t="n">
-        <v>8.781177996797858</v>
+        <v>1.426941424479652</v>
       </c>
       <c r="F6" t="n">
-        <v>7.892301056613245</v>
+        <v>1.282498921699653</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.60951927677372</v>
+        <v>5.13654688247573</v>
       </c>
       <c r="D7" t="n">
-        <v>31.72743542634348</v>
+        <v>5.155708256780816</v>
       </c>
       <c r="E7" t="n">
-        <v>8.781177996797858</v>
+        <v>1.426941424479652</v>
       </c>
       <c r="F7" t="n">
-        <v>7.892301056613245</v>
+        <v>1.282498921699653</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.84908549912139</v>
+        <v>5.337976393607227</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96114602202935</v>
+        <v>5.356186228579769</v>
       </c>
       <c r="E8" t="n">
-        <v>8.781177996797858</v>
+        <v>1.426941424479652</v>
       </c>
       <c r="F8" t="n">
-        <v>7.892301056613245</v>
+        <v>1.282498921699653</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.15982305661971</v>
+        <v>2.950971246700703</v>
       </c>
       <c r="D9" t="n">
-        <v>18.23718106682423</v>
+        <v>2.963541923358937</v>
       </c>
       <c r="E9" t="n">
-        <v>8.781177996797858</v>
+        <v>1.426941424479652</v>
       </c>
       <c r="F9" t="n">
-        <v>7.892301056613245</v>
+        <v>1.282498921699653</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
